--- a/.data/output/destino.xlsx
+++ b/.data/output/destino.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\migue\Documents\remote\personal\rpa_tarea2\rpa-excel-ui-automation\.data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB297ADD-D362-4272-9E52-F88A9B2F5029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{067513F5-C047-4368-A534-6B71547FF51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
